--- a/Datasheet cross referencing/links.xlsx
+++ b/Datasheet cross referencing/links.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28429"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Github\SI5351 library\si5351EasyLib\Datasheet cross referencing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC21A0CC-ED6B-4AEF-B7C9-F0A47F69D141}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA246E96-A32B-4E1A-B980-8DC507B07617}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>Link</t>
   </si>
@@ -67,13 +67,19 @@
   </si>
   <si>
     <t>https://www.skyworksinc.com/-/media/Skyworks/SL/documents/public/application-notes/AN619.pdf</t>
+  </si>
+  <si>
+    <t>https://www.skyworksinc.com/-/media/Skyworks/SL/documents/public/application-notes/AN551.pdf</t>
+  </si>
+  <si>
+    <t>(AN551) CRYSTAL SELECTION GUIDE FOR Si5350/51 DEVICES</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -94,6 +100,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -161,11 +173,11 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -204,8 +216,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9E38F8FF-D7D0-4EF9-B1B5-F2B5B4DFC319}" name="Table1" displayName="Table1" ref="F5:G11" totalsRowShown="0">
-  <autoFilter ref="F5:G11" xr:uid="{9E38F8FF-D7D0-4EF9-B1B5-F2B5B4DFC319}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9E38F8FF-D7D0-4EF9-B1B5-F2B5B4DFC319}" name="Table1" displayName="Table1" ref="F5:G12" totalsRowShown="0">
+  <autoFilter ref="F5:G12" xr:uid="{9E38F8FF-D7D0-4EF9-B1B5-F2B5B4DFC319}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="F6:G11">
     <sortCondition ref="F5:F11"/>
   </sortState>
@@ -480,7 +492,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="F5:G11"/>
+  <dimension ref="F5:G12"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="6" max="6" width="77.77734375" bestFit="1" customWidth="1"/>
@@ -496,18 +508,18 @@
       </c>
     </row>
     <row r="6" spans="6:7" x14ac:dyDescent="0.3">
-      <c r="F6" s="4" t="s">
+      <c r="F6" t="s">
         <v>6</v>
       </c>
-      <c r="G6" s="7" t="s">
+      <c r="G6" s="6" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="7" spans="6:7" x14ac:dyDescent="0.3">
-      <c r="F7" s="5" t="s">
+      <c r="F7" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="G7" s="8" t="s">
+      <c r="G7" s="7" t="s">
         <v>13</v>
       </c>
     </row>
@@ -536,11 +548,19 @@
       </c>
     </row>
     <row r="11" spans="6:7" x14ac:dyDescent="0.3">
-      <c r="F11" s="6" t="s">
+      <c r="F11" s="5" t="s">
         <v>4</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F12" t="s">
+        <v>15</v>
+      </c>
+      <c r="G12" s="8" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
